--- a/xlsx/換色紀錄表(2412) 2號盤存.xlsx
+++ b/xlsx/換色紀錄表(2412) 2號盤存.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1670" documentId="8_{D2DBBC8B-7A72-EE46-B813-F1066388F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B9E16B5-5287-0146-B1EB-EC37E6EA3113}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{8EE62F14-5D2A-BD47-8DCD-EE1D54F2DC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="7" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="7" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="庫存查詢表" sheetId="7" r:id="rId1"/>
@@ -5387,7 +5387,9 @@
     </row>
     <row r="5" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A5" s="125"/>
-      <c r="B5" s="121"/>
+      <c r="B5" s="121">
+        <v>45629</v>
+      </c>
       <c r="C5" s="27" t="s">
         <v>25</v>
       </c>
@@ -5422,7 +5424,9 @@
     </row>
     <row r="6" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A6" s="125"/>
-      <c r="B6" s="121"/>
+      <c r="B6" s="121">
+        <v>45629</v>
+      </c>
       <c r="C6" s="27" t="s">
         <v>26</v>
       </c>
@@ -5457,7 +5461,9 @@
     </row>
     <row r="7" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A7" s="125"/>
-      <c r="B7" s="121"/>
+      <c r="B7" s="121">
+        <v>45629</v>
+      </c>
       <c r="C7" s="27" t="s">
         <v>27</v>
       </c>
@@ -5492,7 +5498,9 @@
     </row>
     <row r="8" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A8" s="125"/>
-      <c r="B8" s="121"/>
+      <c r="B8" s="121">
+        <v>45629</v>
+      </c>
       <c r="C8" s="27" t="s">
         <v>28</v>
       </c>
@@ -5527,7 +5535,9 @@
     </row>
     <row r="9" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A9" s="125"/>
-      <c r="B9" s="121"/>
+      <c r="B9" s="121">
+        <v>45629</v>
+      </c>
       <c r="C9" s="27" t="s">
         <v>29</v>
       </c>
@@ -5597,7 +5607,9 @@
     </row>
     <row r="11" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A11" s="125"/>
-      <c r="B11" s="121"/>
+      <c r="B11" s="121">
+        <v>45630</v>
+      </c>
       <c r="C11" s="27" t="s">
         <v>26</v>
       </c>
@@ -5632,7 +5644,9 @@
     </row>
     <row r="12" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A12" s="125"/>
-      <c r="B12" s="121"/>
+      <c r="B12" s="121">
+        <v>45630</v>
+      </c>
       <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
@@ -5667,7 +5681,9 @@
     </row>
     <row r="13" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A13" s="125"/>
-      <c r="B13" s="121"/>
+      <c r="B13" s="121">
+        <v>45630</v>
+      </c>
       <c r="C13" s="27" t="s">
         <v>28</v>
       </c>
@@ -5777,7 +5793,9 @@
     </row>
     <row r="16" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A16" s="125"/>
-      <c r="B16" s="121"/>
+      <c r="B16" s="121">
+        <v>45632</v>
+      </c>
       <c r="C16" s="27" t="s">
         <v>24</v>
       </c>
@@ -5853,7 +5871,9 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" s="125"/>
-      <c r="B18" s="121"/>
+      <c r="B18" s="121">
+        <v>45635</v>
+      </c>
       <c r="C18" s="27" t="s">
         <v>2</v>
       </c>
@@ -5962,7 +5982,9 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" s="125"/>
-      <c r="B21" s="121"/>
+      <c r="B21" s="121">
+        <v>45637</v>
+      </c>
       <c r="C21" s="27" t="s">
         <v>26</v>
       </c>
@@ -5999,7 +6021,9 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="125"/>
-      <c r="B22" s="121"/>
+      <c r="B22" s="121">
+        <v>45637</v>
+      </c>
       <c r="C22" s="27" t="s">
         <v>29</v>
       </c>
@@ -6036,7 +6060,9 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="125"/>
-      <c r="B23" s="121"/>
+      <c r="B23" s="121">
+        <v>45637</v>
+      </c>
       <c r="C23" s="27" t="s">
         <v>28</v>
       </c>
@@ -6147,7 +6173,9 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" s="125"/>
-      <c r="B26" s="121"/>
+      <c r="B26" s="121">
+        <v>45639</v>
+      </c>
       <c r="C26" s="27" t="s">
         <v>2</v>
       </c>
@@ -6182,7 +6210,9 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" s="125"/>
-      <c r="B27" s="121"/>
+      <c r="B27" s="121">
+        <v>45639</v>
+      </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
       </c>
@@ -6347,7 +6377,9 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="125"/>
-      <c r="B32" s="121"/>
+      <c r="B32" s="121">
+        <v>45643</v>
+      </c>
       <c r="C32" s="27" t="s">
         <v>24</v>
       </c>
@@ -6448,7 +6480,9 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="125"/>
-      <c r="B35" s="121"/>
+      <c r="B35" s="121">
+        <v>45645</v>
+      </c>
       <c r="C35" s="27" t="s">
         <v>24</v>
       </c>
@@ -6619,7 +6653,9 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" s="125"/>
-      <c r="B40" s="121"/>
+      <c r="B40" s="121">
+        <v>45649</v>
+      </c>
       <c r="C40" s="27" t="s">
         <v>27</v>
       </c>
@@ -6654,7 +6690,9 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" s="125"/>
-      <c r="B41" s="121"/>
+      <c r="B41" s="121">
+        <v>45649</v>
+      </c>
       <c r="C41" s="27" t="s">
         <v>29</v>
       </c>
@@ -6685,7 +6723,9 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" s="125"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="121">
+        <v>45649</v>
+      </c>
       <c r="C42" s="27" t="s">
         <v>24</v>
       </c>
@@ -6819,7 +6859,9 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="125"/>
-      <c r="B46" s="158"/>
+      <c r="B46" s="158">
+        <v>45652</v>
+      </c>
       <c r="C46" s="153" t="s">
         <v>24</v>
       </c>
@@ -6852,7 +6894,9 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="125"/>
-      <c r="B47" s="158"/>
+      <c r="B47" s="158">
+        <v>45652</v>
+      </c>
       <c r="C47" s="153" t="s">
         <v>2</v>
       </c>
@@ -6918,7 +6962,9 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" s="125"/>
-      <c r="B49" s="158"/>
+      <c r="B49" s="158">
+        <v>45653</v>
+      </c>
       <c r="C49" s="153" t="s">
         <v>37</v>
       </c>
@@ -6953,7 +6999,9 @@
     </row>
     <row r="50" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="125"/>
-      <c r="B50" s="121"/>
+      <c r="B50" s="158">
+        <v>45653</v>
+      </c>
       <c r="C50" s="157" t="s">
         <v>38</v>
       </c>
@@ -6988,7 +7036,9 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" s="125"/>
-      <c r="B51" s="121"/>
+      <c r="B51" s="158">
+        <v>45653</v>
+      </c>
       <c r="C51" s="27" t="s">
         <v>29</v>
       </c>
@@ -7021,7 +7071,9 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" s="125"/>
-      <c r="B52" s="121"/>
+      <c r="B52" s="158">
+        <v>45653</v>
+      </c>
       <c r="C52" s="27" t="s">
         <v>25</v>
       </c>
@@ -7056,7 +7108,9 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" s="125"/>
-      <c r="B53" s="121"/>
+      <c r="B53" s="158">
+        <v>45653</v>
+      </c>
       <c r="C53" s="27" t="s">
         <v>27</v>
       </c>
@@ -7093,7 +7147,9 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" s="125"/>
-      <c r="B54" s="121"/>
+      <c r="B54" s="158">
+        <v>45653</v>
+      </c>
       <c r="C54" s="27" t="s">
         <v>28</v>
       </c>
@@ -7266,7 +7322,9 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" s="125"/>
-      <c r="B59" s="121"/>
+      <c r="B59" s="121">
+        <v>45657</v>
+      </c>
       <c r="C59" s="27" t="s">
         <v>2</v>
       </c>
@@ -7304,7 +7362,9 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" s="125"/>
-      <c r="B60" s="121"/>
+      <c r="B60" s="121">
+        <v>45657</v>
+      </c>
       <c r="C60" s="27" t="s">
         <v>24</v>
       </c>
@@ -7543,7 +7603,9 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" s="125"/>
-      <c r="B67" s="122"/>
+      <c r="B67" s="121">
+        <v>45663</v>
+      </c>
       <c r="C67" s="34" t="s">
         <v>2</v>
       </c>
@@ -7580,7 +7642,9 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" s="125"/>
-      <c r="B68" s="122"/>
+      <c r="B68" s="121">
+        <v>45663</v>
+      </c>
       <c r="C68" s="34" t="s">
         <v>28</v>
       </c>
@@ -7615,7 +7679,9 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" s="125"/>
-      <c r="B69" s="122"/>
+      <c r="B69" s="121">
+        <v>45663</v>
+      </c>
       <c r="C69" s="34" t="s">
         <v>27</v>
       </c>
@@ -7788,7 +7854,9 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A74" s="125"/>
-      <c r="B74" s="122"/>
+      <c r="B74" s="122">
+        <v>45667</v>
+      </c>
       <c r="C74" s="34" t="s">
         <v>2</v>
       </c>
@@ -7823,7 +7891,9 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A75" s="125"/>
-      <c r="B75" s="122"/>
+      <c r="B75" s="122">
+        <v>45667</v>
+      </c>
       <c r="C75" s="34" t="s">
         <v>29</v>
       </c>
@@ -7957,7 +8027,9 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A79" s="125"/>
-      <c r="B79" s="122"/>
+      <c r="B79" s="122">
+        <v>45670</v>
+      </c>
       <c r="C79" s="34" t="s">
         <v>2</v>
       </c>
@@ -8060,7 +8132,9 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A82" s="125"/>
-      <c r="B82" s="122"/>
+      <c r="B82" s="122">
+        <v>45672</v>
+      </c>
       <c r="C82" s="34" t="s">
         <v>41</v>
       </c>
@@ -8097,7 +8171,9 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A83" s="125"/>
-      <c r="B83" s="122"/>
+      <c r="B83" s="122">
+        <v>45672</v>
+      </c>
       <c r="C83" s="34" t="s">
         <v>42</v>
       </c>
@@ -8130,7 +8206,9 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A84" s="125"/>
-      <c r="B84" s="122"/>
+      <c r="B84" s="122">
+        <v>45672</v>
+      </c>
       <c r="C84" s="34" t="s">
         <v>29</v>
       </c>
@@ -8161,7 +8239,9 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A85" s="125"/>
-      <c r="B85" s="122"/>
+      <c r="B85" s="122">
+        <v>45672</v>
+      </c>
       <c r="C85" s="34" t="s">
         <v>28</v>
       </c>
@@ -8192,7 +8272,9 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A86" s="125"/>
-      <c r="B86" s="122"/>
+      <c r="B86" s="122">
+        <v>45672</v>
+      </c>
       <c r="C86" s="34" t="s">
         <v>24</v>
       </c>
@@ -8262,7 +8344,9 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A88" s="125"/>
-      <c r="B88" s="122"/>
+      <c r="B88" s="122">
+        <v>45673</v>
+      </c>
       <c r="C88" s="34" t="s">
         <v>41</v>
       </c>
@@ -8468,7 +8552,9 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A94" s="125"/>
-      <c r="B94" s="122"/>
+      <c r="B94" s="122">
+        <v>45678</v>
+      </c>
       <c r="C94" s="34" t="s">
         <v>29</v>
       </c>
@@ -8540,7 +8626,9 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A96" s="125"/>
-      <c r="B96" s="122"/>
+      <c r="B96" s="122">
+        <v>45679</v>
+      </c>
       <c r="C96" s="34" t="s">
         <v>27</v>
       </c>
@@ -8573,7 +8661,9 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A97" s="125"/>
-      <c r="B97" s="122"/>
+      <c r="B97" s="122">
+        <v>45679</v>
+      </c>
       <c r="C97" s="34" t="s">
         <v>25</v>
       </c>
@@ -8608,7 +8698,9 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A98" s="125"/>
-      <c r="B98" s="122"/>
+      <c r="B98" s="122">
+        <v>45679</v>
+      </c>
       <c r="C98" s="34" t="s">
         <v>37</v>
       </c>
@@ -8643,7 +8735,9 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A99" s="125"/>
-      <c r="B99" s="122"/>
+      <c r="B99" s="122">
+        <v>45679</v>
+      </c>
       <c r="C99" s="34" t="s">
         <v>24</v>
       </c>
@@ -8676,7 +8770,9 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A100" s="125"/>
-      <c r="B100" s="122"/>
+      <c r="B100" s="122">
+        <v>45679</v>
+      </c>
       <c r="C100" s="34" t="s">
         <v>29</v>
       </c>
@@ -8748,7 +8844,9 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A102" s="125"/>
-      <c r="B102" s="122"/>
+      <c r="B102" s="122">
+        <v>45680</v>
+      </c>
       <c r="C102" s="34" t="s">
         <v>2</v>
       </c>
@@ -8816,7 +8914,9 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A104" s="125"/>
-      <c r="B104" s="122"/>
+      <c r="B104" s="122">
+        <v>45691</v>
+      </c>
       <c r="C104" s="34" t="s">
         <v>29</v>
       </c>
@@ -8851,7 +8951,9 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A105" s="125"/>
-      <c r="B105" s="122"/>
+      <c r="B105" s="122">
+        <v>45691</v>
+      </c>
       <c r="C105" s="34" t="s">
         <v>31</v>
       </c>
@@ -8886,7 +8988,9 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A106" s="125"/>
-      <c r="B106" s="122"/>
+      <c r="B106" s="122">
+        <v>45691</v>
+      </c>
       <c r="C106" s="34" t="s">
         <v>43</v>
       </c>
@@ -8919,7 +9023,9 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A107" s="125"/>
-      <c r="B107" s="122"/>
+      <c r="B107" s="122">
+        <v>45691</v>
+      </c>
       <c r="C107" s="34" t="s">
         <v>44</v>
       </c>
@@ -8954,7 +9060,9 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A108" s="125"/>
-      <c r="B108" s="122"/>
+      <c r="B108" s="122">
+        <v>45691</v>
+      </c>
       <c r="C108" s="34" t="s">
         <v>2</v>
       </c>
@@ -9561,7 +9669,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45755</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
